--- a/submission/knowledge/A02-武汉景点讲解员/武汉景点讲解员QA导入表.xlsx
+++ b/submission/knowledge/A02-武汉景点讲解员/武汉景点讲解员QA导入表.xlsx
@@ -979,6 +979,295 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辛亥革命纪念馆要预约吗？</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">院方须知：个人凭有效证件现场有序入馆，无须网上预约；有接待上限。团体讲解要预约。南北区错峰闭馆日不同。</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辛亥</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">红楼周一开吗？</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">北区（红楼）须知：每周二闭馆，周三至周一开放。南区周一闭馆。以官网当天为准。</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辛亥</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">免费吗？</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参观免费。须知写部分复原陈列和讲解可能收费，看院内公告。</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辛亥</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川阁收费吗？</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">管理处须知写博物馆常年免费开放。个人以官网和公众号当天为准；夜游常另计。咨询027-84710887。</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川阁周一开吗？</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">须知：每周一闭馆；周四15:00可能闭馆维护；除夕闭馆。法定假日另有安排。</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武大樱花怎么进？</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">学校不是景区。赏樱期走官网或官方微信预约，免费限额。以当年校园管理通告为准，拒黄牛。</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武大</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">和东湖樱园一张票吗？</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不是。东湖樱花园常单独售票；武大是校园预约。</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武大</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩要门票吗？</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公共滨江空间一般免费。汉口、武昌、汉阳江滩不是同一个点。</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖绿道要买票吗？</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听涛沿岸和绿道常可游憩。园中园另计。以管委会为准。</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">绿道</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">樱花哪天最好？</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每年不同。看「游东湖」和学校通告，我不编日期。</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">花期</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖游船多少钱？</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以「游东湖」和窗口当天为准。不是长江夜游，也不是通勤轮渡。</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">游船</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖门票含欢乐谷吗？</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不含。欢乐谷、海洋世界、植物园独立购票。</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">欢乐谷</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老人必须登顶吗？</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不必。蛇山有台阶，可只游园或看江。满载听公园预警。</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">登楼</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">园博园在东湖吗？</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不在。在东西湖金银湖一带，要跨区。</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">园博</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中山舰在黄鹤楼附近吗？</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在江夏金口一带，不是武昌半日点。</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中山舰</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">磨山索道一定开吗？</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以当天项目方和「游东湖」为准，不打包。</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">索道</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日场票晚上能登楼吗？</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能默认。夜上黄鹤楼另票。</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜场</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>